--- a/branches/dev/CodeSystem-mii-cs-seltene-narse-therapietyp.xlsx
+++ b/branches/dev/CodeSystem-mii-cs-seltene-narse-therapietyp.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T10:39:42+00:00</t>
+    <t>2026-07-23T11:20:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/CodeSystem-mii-cs-seltene-narse-therapietyp.xlsx
+++ b/branches/dev/CodeSystem-mii-cs-seltene-narse-therapietyp.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T11:20:28+00:00</t>
+    <t>2026-07-23T15:55:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/CodeSystem-mii-cs-seltene-narse-therapietyp.xlsx
+++ b/branches/dev/CodeSystem-mii-cs-seltene-narse-therapietyp.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T15:55:45+00:00</t>
+    <t>2026-07-24T06:29:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/CodeSystem-mii-cs-seltene-narse-therapietyp.xlsx
+++ b/branches/dev/CodeSystem-mii-cs-seltene-narse-therapietyp.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2026.0.1</t>
+    <t>2027.0.0-ballot.rc1</t>
   </si>
   <si>
     <t>Name</t>
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-24T06:29:13+00:00</t>
+    <t>2026-09-03T10:43:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -79,7 +79,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t/>
+    <t>Germany</t>
   </si>
   <si>
     <t>Description</t>

--- a/branches/dev/CodeSystem-mii-cs-seltene-narse-therapietyp.xlsx
+++ b/branches/dev/CodeSystem-mii-cs-seltene-narse-therapietyp.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T10:43:48+00:00</t>
+    <t>2026-09-03T17:01:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/CodeSystem-mii-cs-seltene-narse-therapietyp.xlsx
+++ b/branches/dev/CodeSystem-mii-cs-seltene-narse-therapietyp.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T17:01:55+00:00</t>
+    <t>2026-09-04T05:29:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/CodeSystem-mii-cs-seltene-narse-therapietyp.xlsx
+++ b/branches/dev/CodeSystem-mii-cs-seltene-narse-therapietyp.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T05:29:06+00:00</t>
+    <t>2026-09-04T06:37:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/CodeSystem-mii-cs-seltene-narse-therapietyp.xlsx
+++ b/branches/dev/CodeSystem-mii-cs-seltene-narse-therapietyp.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T06:37:14+00:00</t>
+    <t>2026-09-04T07:02:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/CodeSystem-mii-cs-seltene-narse-therapietyp.xlsx
+++ b/branches/dev/CodeSystem-mii-cs-seltene-narse-therapietyp.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T07:02:52+00:00</t>
+    <t>2026-09-04T08:01:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/CodeSystem-mii-cs-seltene-narse-therapietyp.xlsx
+++ b/branches/dev/CodeSystem-mii-cs-seltene-narse-therapietyp.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T08:01:15+00:00</t>
+    <t>2026-09-04T11:35:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/CodeSystem-mii-cs-seltene-narse-therapietyp.xlsx
+++ b/branches/dev/CodeSystem-mii-cs-seltene-narse-therapietyp.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T11:35:42+00:00</t>
+    <t>2026-09-04T11:52:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/CodeSystem-mii-cs-seltene-narse-therapietyp.xlsx
+++ b/branches/dev/CodeSystem-mii-cs-seltene-narse-therapietyp.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T11:52:20+00:00</t>
+    <t>2026-09-04T12:44:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/CodeSystem-mii-cs-seltene-narse-therapietyp.xlsx
+++ b/branches/dev/CodeSystem-mii-cs-seltene-narse-therapietyp.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T12:44:12+00:00</t>
+    <t>2026-09-04T13:01:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/CodeSystem-mii-cs-seltene-narse-therapietyp.xlsx
+++ b/branches/dev/CodeSystem-mii-cs-seltene-narse-therapietyp.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T13:01:37+00:00</t>
+    <t>2026-09-04T16:11:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/CodeSystem-mii-cs-seltene-narse-therapietyp.xlsx
+++ b/branches/dev/CodeSystem-mii-cs-seltene-narse-therapietyp.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T16:11:50+00:00</t>
+    <t>2026-09-04T16:57:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/CodeSystem-mii-cs-seltene-narse-therapietyp.xlsx
+++ b/branches/dev/CodeSystem-mii-cs-seltene-narse-therapietyp.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T16:57:12+00:00</t>
+    <t>2026-09-07T15:50:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/CodeSystem-mii-cs-seltene-narse-therapietyp.xlsx
+++ b/branches/dev/CodeSystem-mii-cs-seltene-narse-therapietyp.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T15:50:41+00:00</t>
+    <t>2026-09-07T16:06:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/CodeSystem-mii-cs-seltene-narse-therapietyp.xlsx
+++ b/branches/dev/CodeSystem-mii-cs-seltene-narse-therapietyp.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T16:06:13+00:00</t>
+    <t>2026-09-08T09:14:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/CodeSystem-mii-cs-seltene-narse-therapietyp.xlsx
+++ b/branches/dev/CodeSystem-mii-cs-seltene-narse-therapietyp.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T09:14:37+00:00</t>
+    <t>2026-09-08T09:32:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/CodeSystem-mii-cs-seltene-narse-therapietyp.xlsx
+++ b/branches/dev/CodeSystem-mii-cs-seltene-narse-therapietyp.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T09:32:56+00:00</t>
+    <t>2026-09-08T15:03:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/CodeSystem-mii-cs-seltene-narse-therapietyp.xlsx
+++ b/branches/dev/CodeSystem-mii-cs-seltene-narse-therapietyp.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T15:03:47+00:00</t>
+    <t>2026-09-09T09:29:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/CodeSystem-mii-cs-seltene-narse-therapietyp.xlsx
+++ b/branches/dev/CodeSystem-mii-cs-seltene-narse-therapietyp.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T09:29:55+00:00</t>
+    <t>2026-09-09T10:02:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/CodeSystem-mii-cs-seltene-narse-therapietyp.xlsx
+++ b/branches/dev/CodeSystem-mii-cs-seltene-narse-therapietyp.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T10:02:49+00:00</t>
+    <t>2026-09-09T11:08:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/CodeSystem-mii-cs-seltene-narse-therapietyp.xlsx
+++ b/branches/dev/CodeSystem-mii-cs-seltene-narse-therapietyp.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T11:08:17+00:00</t>
+    <t>2026-09-09T11:49:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/CodeSystem-mii-cs-seltene-narse-therapietyp.xlsx
+++ b/branches/dev/CodeSystem-mii-cs-seltene-narse-therapietyp.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T11:49:20+00:00</t>
+    <t>2026-09-11T10:52:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/CodeSystem-mii-cs-seltene-narse-therapietyp.xlsx
+++ b/branches/dev/CodeSystem-mii-cs-seltene-narse-therapietyp.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-11T10:52:45+00:00</t>
+    <t>2026-09-11T12:45:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/CodeSystem-mii-cs-seltene-narse-therapietyp.xlsx
+++ b/branches/dev/CodeSystem-mii-cs-seltene-narse-therapietyp.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-11T12:45:52+00:00</t>
+    <t>2026-09-11T14:10:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
